--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T10:00:28+00:00</t>
+    <t>2025-07-07T12:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T12:38:35+00:00</t>
+    <t>2025-07-07T15:58:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:58:33+00:00</t>
+    <t>2025-07-07T16:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
